--- a/New folder/(RM)Raw_Material_Purchase_Oder_Planning/GTG_daily_stock_analysis/Item_wise_order_calculation_per_month_in_kg_CONNECTED/temp_out_of_monthly_4.xlsx
+++ b/New folder/(RM)Raw_Material_Purchase_Oder_Planning/GTG_daily_stock_analysis/Item_wise_order_calculation_per_month_in_kg_CONNECTED/temp_out_of_monthly_4.xlsx
@@ -466,7 +466,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5159.1756</v>
+        <v>4801.0584</v>
       </c>
       <c r="C4" t="n">
         <v>54.768</v>
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12195.17632</v>
+        <v>11990.14632</v>
       </c>
       <c r="C5" t="n">
         <v>571.6600000000001</v>
@@ -531,10 +531,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>234.8325</v>
+        <v>203.8365</v>
       </c>
       <c r="C9" t="n">
-        <v>14.5629</v>
+        <v>6.4629</v>
       </c>
     </row>
     <row r="10">
